--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>59.43438</v>
+      </c>
+      <c r="C2">
+        <v>95.56828</v>
+      </c>
+      <c r="D2">
+        <v>85.67236</v>
+      </c>
+      <c r="E2">
+        <v>46.94592</v>
+      </c>
+      <c r="F2">
         <v>59.67112</v>
       </c>
-      <c r="C2">
-        <v>59.43438</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>100.2203</v>
       </c>
-      <c r="E2">
-        <v>95.56828</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>102.0309</v>
       </c>
-      <c r="G2">
-        <v>85.67236</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>67.79109</v>
-      </c>
-      <c r="I2">
-        <v>46.94592</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>59.43713</v>
+      </c>
+      <c r="C3">
+        <v>97.35299999999999</v>
+      </c>
+      <c r="D3">
+        <v>80.29993</v>
+      </c>
+      <c r="E3">
+        <v>32.12703</v>
+      </c>
+      <c r="F3">
         <v>59.56623</v>
       </c>
-      <c r="C3">
-        <v>59.43713</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>104.4999</v>
       </c>
-      <c r="E3">
-        <v>97.35299999999999</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>99.86367</v>
       </c>
-      <c r="G3">
-        <v>80.29993</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>44.12851</v>
-      </c>
-      <c r="I3">
-        <v>32.12703</v>
       </c>
     </row>
     <row r="4">
@@ -473,25 +473,25 @@
         <v>59.20792</v>
       </c>
       <c r="C4">
+        <v>97.61635</v>
+      </c>
+      <c r="D4">
+        <v>88.82235</v>
+      </c>
+      <c r="E4">
+        <v>41.08108</v>
+      </c>
+      <c r="F4">
         <v>59.20792</v>
       </c>
-      <c r="D4">
+      <c r="G4">
         <v>101.5891</v>
       </c>
-      <c r="E4">
-        <v>97.61635</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>98.00399</v>
       </c>
-      <c r="G4">
-        <v>88.82235</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>52.75676</v>
-      </c>
-      <c r="I4">
-        <v>41.08108</v>
       </c>
     </row>
     <row r="5">
@@ -504,25 +504,25 @@
         <v>68.25397</v>
       </c>
       <c r="C5">
+        <v>98.33334000000001</v>
+      </c>
+      <c r="D5">
+        <v>88.41202</v>
+      </c>
+      <c r="E5">
+        <v>34.48276</v>
+      </c>
+      <c r="F5">
         <v>68.25397</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>102.9167</v>
       </c>
-      <c r="E5">
-        <v>98.33334000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>97.85408</v>
       </c>
-      <c r="G5">
-        <v>88.41202</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>45.8886</v>
-      </c>
-      <c r="I5">
-        <v>34.48276</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>59.81567</v>
+      </c>
+      <c r="C6">
+        <v>96.40188000000001</v>
+      </c>
+      <c r="D6">
+        <v>86.05166</v>
+      </c>
+      <c r="E6">
+        <v>37.97009</v>
+      </c>
+      <c r="F6">
         <v>59.93087</v>
       </c>
-      <c r="C6">
-        <v>59.81567</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>100.226</v>
       </c>
-      <c r="E6">
-        <v>96.40188000000001</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>100.5535</v>
       </c>
-      <c r="G6">
-        <v>86.05166</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>57.35043</v>
-      </c>
-      <c r="I6">
-        <v>37.97009</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>64.08759000000001</v>
+      </c>
+      <c r="C7">
+        <v>97.29425000000001</v>
+      </c>
+      <c r="D7">
+        <v>84.05466</v>
+      </c>
+      <c r="E7">
+        <v>35.79487</v>
+      </c>
+      <c r="F7">
         <v>64.23357</v>
       </c>
-      <c r="C7">
-        <v>64.08759000000001</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>103.4949</v>
       </c>
-      <c r="E7">
-        <v>97.29425000000001</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>105.6948</v>
       </c>
-      <c r="G7">
-        <v>84.05466</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>49.74359</v>
-      </c>
-      <c r="I7">
-        <v>35.79487</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>61.15242</v>
+      </c>
+      <c r="C8">
+        <v>95.57195</v>
+      </c>
+      <c r="D8">
+        <v>87.70161</v>
+      </c>
+      <c r="E8">
+        <v>36.42794</v>
+      </c>
+      <c r="F8">
         <v>61.33829</v>
       </c>
-      <c r="C8">
-        <v>61.15242</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>100</v>
       </c>
-      <c r="E8">
-        <v>95.57195</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>104.0323</v>
       </c>
-      <c r="G8">
-        <v>87.70161</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>48.71795</v>
-      </c>
-      <c r="I8">
-        <v>36.42794</v>
       </c>
     </row>
     <row r="9">
@@ -628,25 +628,25 @@
         <v>55.15789</v>
       </c>
       <c r="C9">
+        <v>96.68471</v>
+      </c>
+      <c r="D9">
+        <v>81.69399</v>
+      </c>
+      <c r="E9">
+        <v>34.08788</v>
+      </c>
+      <c r="F9">
         <v>55.15789</v>
       </c>
-      <c r="D9">
+      <c r="G9">
         <v>103.7889</v>
       </c>
-      <c r="E9">
-        <v>96.68471</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>95.08197</v>
       </c>
-      <c r="G9">
-        <v>81.69399</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>46.00533</v>
-      </c>
-      <c r="I9">
-        <v>34.08788</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>58.24648</v>
+      </c>
+      <c r="C10">
+        <v>96.62690000000001</v>
+      </c>
+      <c r="D10">
+        <v>84.88</v>
+      </c>
+      <c r="E10">
+        <v>33.79835</v>
+      </c>
+      <c r="F10">
         <v>58.33844</v>
       </c>
-      <c r="C10">
-        <v>58.24648</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.9667</v>
       </c>
-      <c r="E10">
-        <v>96.62690000000001</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>101.04</v>
       </c>
-      <c r="G10">
-        <v>84.88</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>46.52293</v>
-      </c>
-      <c r="I10">
-        <v>33.79835</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>57.19558</v>
+      </c>
+      <c r="C11">
+        <v>97.22221999999999</v>
+      </c>
+      <c r="D11">
+        <v>82.70547999999999</v>
+      </c>
+      <c r="E11">
+        <v>33.9207</v>
+      </c>
+      <c r="F11">
         <v>57.19557</v>
       </c>
-      <c r="C11">
-        <v>57.19558</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>103.7326</v>
       </c>
-      <c r="E11">
-        <v>97.22221999999999</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>97.08904</v>
       </c>
-      <c r="G11">
-        <v>82.70547999999999</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>47.57709</v>
-      </c>
-      <c r="I11">
-        <v>33.9207</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>57.6544</v>
+      </c>
+      <c r="C12">
+        <v>97.1254</v>
+      </c>
+      <c r="D12">
+        <v>84.07590999999999</v>
+      </c>
+      <c r="E12">
+        <v>40.05757</v>
+      </c>
+      <c r="F12">
         <v>57.75296</v>
       </c>
-      <c r="C12">
-        <v>57.6544</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>102.3087</v>
       </c>
-      <c r="E12">
-        <v>97.1254</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>102.599</v>
       </c>
-      <c r="G12">
-        <v>84.07590999999999</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>56.99734</v>
-      </c>
-      <c r="I12">
-        <v>40.05757</v>
       </c>
     </row>
     <row r="13">
@@ -752,25 +752,25 @@
         <v>62.81407</v>
       </c>
       <c r="C13">
+        <v>97.2043</v>
+      </c>
+      <c r="D13">
+        <v>82.40343</v>
+      </c>
+      <c r="E13">
+        <v>35.20971</v>
+      </c>
+      <c r="F13">
         <v>62.81407</v>
       </c>
-      <c r="D13">
+      <c r="G13">
         <v>102.043</v>
       </c>
-      <c r="E13">
-        <v>97.2043</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>94.84978</v>
       </c>
-      <c r="G13">
-        <v>82.40343</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>44.81236</v>
-      </c>
-      <c r="I13">
-        <v>35.20971</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +783,25 @@
         <v>60.07463</v>
       </c>
       <c r="C14">
+        <v>96.438</v>
+      </c>
+      <c r="D14">
+        <v>83.80952000000001</v>
+      </c>
+      <c r="E14">
+        <v>44.05941</v>
+      </c>
+      <c r="F14">
         <v>60.07463</v>
       </c>
-      <c r="D14">
+      <c r="G14">
         <v>102.2427</v>
       </c>
-      <c r="E14">
-        <v>96.438</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>92.14286</v>
       </c>
-      <c r="G14">
-        <v>83.80952000000001</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>57.05445</v>
-      </c>
-      <c r="I14">
-        <v>44.05941</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>61.15602</v>
+      </c>
+      <c r="C15">
+        <v>96.03804</v>
+      </c>
+      <c r="D15">
+        <v>84.59079</v>
+      </c>
+      <c r="E15">
+        <v>40.1441</v>
+      </c>
+      <c r="F15">
         <v>61.43416</v>
       </c>
-      <c r="C15">
-        <v>61.15602</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>101.6275</v>
       </c>
-      <c r="E15">
-        <v>96.03804</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>103.4466</v>
       </c>
-      <c r="G15">
-        <v>84.59079</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>57.81149</v>
-      </c>
-      <c r="I15">
-        <v>40.1441</v>
       </c>
     </row>
     <row r="16">
@@ -845,25 +845,25 @@
         <v>67.58064</v>
       </c>
       <c r="C16">
+        <v>96.75785</v>
+      </c>
+      <c r="D16">
+        <v>86.51877</v>
+      </c>
+      <c r="E16">
+        <v>44.07583</v>
+      </c>
+      <c r="F16">
         <v>67.58064</v>
       </c>
-      <c r="D16">
+      <c r="G16">
         <v>100.304</v>
       </c>
-      <c r="E16">
-        <v>96.75785</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>98.29352</v>
       </c>
-      <c r="G16">
-        <v>86.51877</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>57.34597</v>
-      </c>
-      <c r="I16">
-        <v>44.07583</v>
       </c>
     </row>
     <row r="17">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>70</v>
+      </c>
+      <c r="C17">
+        <v>96.70959000000001</v>
+      </c>
+      <c r="D17">
+        <v>86.54353</v>
+      </c>
+      <c r="E17">
+        <v>46.51494</v>
+      </c>
+      <c r="F17">
         <v>70.45453999999999</v>
       </c>
-      <c r="C17">
-        <v>70</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>102.0029</v>
       </c>
-      <c r="E17">
-        <v>96.70959000000001</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>97.09763</v>
       </c>
-      <c r="G17">
-        <v>86.54353</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>60.02845</v>
-      </c>
-      <c r="I17">
-        <v>46.51494</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>59.63995</v>
+      </c>
+      <c r="C18">
+        <v>94.95323</v>
+      </c>
+      <c r="D18">
+        <v>85.02567999999999</v>
+      </c>
+      <c r="E18">
+        <v>35.53936</v>
+      </c>
+      <c r="F18">
         <v>59.81417</v>
       </c>
-      <c r="C18">
-        <v>59.63995</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>101.1691</v>
       </c>
-      <c r="E18">
-        <v>94.95323</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>107.2699</v>
       </c>
-      <c r="G18">
-        <v>85.02567999999999</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>50.37442</v>
-      </c>
-      <c r="I18">
-        <v>35.53936</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>64.17113000000001</v>
+      </c>
+      <c r="C19">
+        <v>96.41576999999999</v>
+      </c>
+      <c r="D19">
+        <v>82.70945</v>
+      </c>
+      <c r="E19">
+        <v>33.33334</v>
+      </c>
+      <c r="F19">
         <v>64.30481</v>
       </c>
-      <c r="C19">
-        <v>64.17113000000001</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>100.5376</v>
       </c>
-      <c r="E19">
-        <v>96.41576999999999</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>95.00891</v>
       </c>
-      <c r="G19">
-        <v>82.70945</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>44.85363</v>
-      </c>
-      <c r="I19">
-        <v>33.33334</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>64.54018000000001</v>
+      </c>
+      <c r="C20">
+        <v>96.80789</v>
+      </c>
+      <c r="D20">
+        <v>85.877</v>
+      </c>
+      <c r="E20">
+        <v>38.27446</v>
+      </c>
+      <c r="F20">
         <v>64.70587999999999</v>
       </c>
-      <c r="C20">
-        <v>64.54018000000001</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>101.451</v>
       </c>
-      <c r="E20">
-        <v>96.80789</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>101.7084</v>
       </c>
-      <c r="G20">
-        <v>85.877</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>54.54546</v>
-      </c>
-      <c r="I20">
-        <v>38.27446</v>
       </c>
     </row>
     <row r="21">
@@ -1000,25 +1000,25 @@
         <v>64.14182</v>
       </c>
       <c r="C21">
+        <v>95.76862</v>
+      </c>
+      <c r="D21">
+        <v>86.63316</v>
+      </c>
+      <c r="E21">
+        <v>37.1488</v>
+      </c>
+      <c r="F21">
         <v>64.14182</v>
       </c>
-      <c r="D21">
+      <c r="G21">
         <v>100.6963</v>
       </c>
-      <c r="E21">
-        <v>95.76862</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>100.3015</v>
       </c>
-      <c r="G21">
-        <v>86.63316</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>50.20812</v>
-      </c>
-      <c r="I21">
-        <v>37.1488</v>
       </c>
     </row>
     <row r="22">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>59.58442</v>
+      </c>
+      <c r="C22">
+        <v>96.44473000000001</v>
+      </c>
+      <c r="D22">
+        <v>85.76873999999999</v>
+      </c>
+      <c r="E22">
+        <v>34.2966</v>
+      </c>
+      <c r="F22">
         <v>59.68831</v>
       </c>
-      <c r="C22">
-        <v>59.58442</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>100.808</v>
       </c>
-      <c r="E22">
-        <v>96.44473000000001</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>97.20457</v>
       </c>
-      <c r="G22">
-        <v>85.76873999999999</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>47.06256</v>
-      </c>
-      <c r="I22">
-        <v>34.2966</v>
       </c>
     </row>
     <row r="23">
@@ -1059,28 +1059,28 @@
         </is>
       </c>
       <c r="B23">
+        <v>56.88074</v>
+      </c>
+      <c r="C23">
+        <v>97.17646999999999</v>
+      </c>
+      <c r="D23">
+        <v>84.90566</v>
+      </c>
+      <c r="E23">
+        <v>50.11601</v>
+      </c>
+      <c r="F23">
         <v>56.88073</v>
       </c>
-      <c r="C23">
-        <v>56.88074</v>
-      </c>
-      <c r="D23">
+      <c r="G23">
         <v>103.2941</v>
       </c>
-      <c r="E23">
-        <v>97.17646999999999</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>99.0566</v>
       </c>
-      <c r="G23">
-        <v>84.90566</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>61.71694</v>
-      </c>
-      <c r="I23">
-        <v>50.11601</v>
       </c>
     </row>
     <row r="24">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B24">
+        <v>69.06207000000001</v>
+      </c>
+      <c r="C24">
+        <v>97.35048999999999</v>
+      </c>
+      <c r="D24">
+        <v>82.41042</v>
+      </c>
+      <c r="E24">
+        <v>41.93755</v>
+      </c>
+      <c r="F24">
         <v>69.25517000000001</v>
       </c>
-      <c r="C24">
-        <v>69.06207000000001</v>
-      </c>
-      <c r="D24">
+      <c r="G24">
         <v>103.2447</v>
       </c>
-      <c r="E24">
-        <v>97.35048999999999</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>105.6098</v>
       </c>
-      <c r="G24">
-        <v>82.41042</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>61.85331</v>
-      </c>
-      <c r="I24">
-        <v>41.93755</v>
       </c>
     </row>
     <row r="25">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>61.48868</v>
+      </c>
+      <c r="C25">
+        <v>96.48454</v>
+      </c>
+      <c r="D25">
+        <v>78.65546000000001</v>
+      </c>
+      <c r="E25">
+        <v>31.46571</v>
+      </c>
+      <c r="F25">
         <v>61.5534</v>
       </c>
-      <c r="C25">
-        <v>61.48868</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>102.5413</v>
       </c>
-      <c r="E25">
-        <v>96.48454</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>100.4202</v>
       </c>
-      <c r="G25">
-        <v>78.65546000000001</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>44.68848</v>
-      </c>
-      <c r="I25">
-        <v>31.46571</v>
       </c>
     </row>
     <row r="26">
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>61.02719</v>
+      </c>
+      <c r="C26">
+        <v>96.31682000000001</v>
+      </c>
+      <c r="D26">
+        <v>83.94524</v>
+      </c>
+      <c r="E26">
+        <v>29.10798</v>
+      </c>
+      <c r="F26">
         <v>61.07754</v>
       </c>
-      <c r="C26">
-        <v>61.02719</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>101.1082</v>
       </c>
-      <c r="E26">
-        <v>96.31682000000001</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>101.8668</v>
       </c>
-      <c r="G26">
-        <v>83.94524</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>39.83904</v>
-      </c>
-      <c r="I26">
-        <v>29.10798</v>
       </c>
     </row>
     <row r="27">
@@ -1186,25 +1186,25 @@
         <v>62.00265</v>
       </c>
       <c r="C27">
+        <v>96.50568</v>
+      </c>
+      <c r="D27">
+        <v>81.17017</v>
+      </c>
+      <c r="E27">
+        <v>39.77888</v>
+      </c>
+      <c r="F27">
         <v>62.00265</v>
       </c>
-      <c r="D27">
+      <c r="G27">
         <v>102.1812</v>
       </c>
-      <c r="E27">
-        <v>96.50568</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>102.5958</v>
       </c>
-      <c r="G27">
-        <v>81.17017</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>52.50451</v>
-      </c>
-      <c r="I27">
-        <v>39.77888</v>
       </c>
     </row>
     <row r="28">
@@ -1217,25 +1217,25 @@
         <v>60.24531</v>
       </c>
       <c r="C28">
+        <v>97.53149000000001</v>
+      </c>
+      <c r="D28">
+        <v>81.73515999999999</v>
+      </c>
+      <c r="E28">
+        <v>32.5138</v>
+      </c>
+      <c r="F28">
         <v>60.24531</v>
       </c>
-      <c r="D28">
+      <c r="G28">
         <v>104.5844</v>
       </c>
-      <c r="E28">
-        <v>97.53149000000001</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>97.07763</v>
       </c>
-      <c r="G28">
-        <v>81.73515999999999</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>41.74611</v>
-      </c>
-      <c r="I28">
-        <v>32.5138</v>
       </c>
     </row>
     <row r="29">
@@ -1245,28 +1245,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>61.32104</v>
+      </c>
+      <c r="C29">
+        <v>96.47199000000001</v>
+      </c>
+      <c r="D29">
+        <v>82.68734000000001</v>
+      </c>
+      <c r="E29">
+        <v>36.71986</v>
+      </c>
+      <c r="F29">
         <v>61.50537</v>
       </c>
-      <c r="C29">
-        <v>61.32104</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>102.3719</v>
       </c>
-      <c r="E29">
-        <v>96.47199000000001</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>101.8088</v>
       </c>
-      <c r="G29">
-        <v>82.68734000000001</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>50.47465</v>
-      </c>
-      <c r="I29">
-        <v>36.71986</v>
       </c>
     </row>
     <row r="30">
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>62.75924</v>
+      </c>
+      <c r="C30">
+        <v>96.75246</v>
+      </c>
+      <c r="D30">
+        <v>82.36633</v>
+      </c>
+      <c r="E30">
+        <v>34.10513</v>
+      </c>
+      <c r="F30">
         <v>62.84941</v>
       </c>
-      <c r="C30">
-        <v>62.75924</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>103.3701</v>
       </c>
-      <c r="E30">
-        <v>96.75246</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>98.52105</v>
       </c>
-      <c r="G30">
-        <v>82.36633</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>48.68586</v>
-      </c>
-      <c r="I30">
-        <v>34.10513</v>
       </c>
     </row>
     <row r="31">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>60.04584</v>
+      </c>
+      <c r="C31">
+        <v>96.44128000000001</v>
+      </c>
+      <c r="D31">
+        <v>80.05808</v>
+      </c>
+      <c r="E31">
+        <v>28.72867</v>
+      </c>
+      <c r="F31">
         <v>60.19862</v>
       </c>
-      <c r="C31">
-        <v>60.04584</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>103.5079</v>
       </c>
-      <c r="E31">
-        <v>96.44128000000001</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>102.6137</v>
       </c>
-      <c r="G31">
-        <v>80.05808</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>40.6164</v>
-      </c>
-      <c r="I31">
-        <v>28.72867</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:38</t>
+    <t xml:space="preserve">2026-08-02 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:39</t>
+    <t xml:space="preserve">2026-08-05 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:31</t>
+    <t xml:space="preserve">2026-08-05 18:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:12</t>
+    <t xml:space="preserve">2026-08-16 09:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:44</t>
+    <t xml:space="preserve">2026-08-19 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:38</t>
+    <t xml:space="preserve">2026-08-28 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:20</t>
+    <t xml:space="preserve">2026-09-06 17:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
